--- a/artfynd/A 18117-2026 artfynd.xlsx
+++ b/artfynd/A 18117-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>119302613</v>
       </c>
       <c r="B2" t="n">
-        <v>97824</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +780,7 @@
         <v>128620034</v>
       </c>
       <c r="B3" t="n">
-        <v>58582</v>
+        <v>58817</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,6 +887,210 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>119302614</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Norr om Stortjärnen, Gstr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>589492</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6766735</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>fuktigt tallungskogsbestånd</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>119302615</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Norr om Stortjärnen, Gstr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>589492</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6766805</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>äldre tallsumpskog</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
